--- a/xls/square_un_16_tri3_19_0.xlsx
+++ b/xls/square_un_16_tri3_19_0.xlsx
@@ -482,13 +482,13 @@
         <v>1596</v>
       </c>
       <c r="I16">
-        <v>-0.5596750328688417</v>
+        <v>-0.5580461576064307</v>
       </c>
       <c r="J16">
-        <v>-1.5761869518332456</v>
+        <v>-1.5760334963829072</v>
       </c>
       <c r="K16">
-        <v>-0.48900447532712626</v>
+        <v>-0.4884279831198797</v>
       </c>
     </row>
   </sheetData>
